--- a/src/assets/worklog/15.VisualInspection.xlsx
+++ b/src/assets/worklog/15.VisualInspection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\data\templates\worklog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D47B282-5FD0-4CD8-9F53-7FB734E0BC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2854EA19-9B1B-4160-B17A-3B3D30DC4873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1425" windowWidth="24705" windowHeight="13965" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
+    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <definedName name="line">원본!$C$9</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
-    <definedName name="productionId">원본!$G$7</definedName>
+    <definedName name="projectId">원본!$G$7</definedName>
     <definedName name="remark">원본!$A$39</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
     <definedName name="safety">원본!$K$36</definedName>
@@ -463,69 +463,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -562,6 +499,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -578,6 +521,63 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -924,17 +924,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,697 +946,743 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="5" t="s">
+      <c r="F7" s="37"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="37"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="3" t="s">
+      <c r="J9" s="37"/>
+      <c r="K9" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22" t="s">
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="26"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="33"/>
+      <c r="E15" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="9"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="12"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="36"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="17"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="25"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="20"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="28"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="17"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="20"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="28"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="17"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="25"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="20"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="28"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="17"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="25"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="20"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="17"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="20"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="28"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="17"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="20"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="26"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="38"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="19"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="41"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
+      <c r="A32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="26"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="5"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="23" t="s">
+      <c r="B33" s="15"/>
+      <c r="C33" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="13" t="s">
+      <c r="D33" s="16"/>
+      <c r="E33" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="13" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="13"/>
-      <c r="K33" s="23" t="s">
+      <c r="J33" s="15"/>
+      <c r="K33" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="14"/>
+      <c r="L33" s="16"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="26"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="5"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14" t="s">
+      <c r="B36" s="15"/>
+      <c r="C36" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="13" t="s">
+      <c r="D36" s="16"/>
+      <c r="E36" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="14" t="s">
+      <c r="F36" s="15"/>
+      <c r="G36" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="13" t="s">
+      <c r="H36" s="16"/>
+      <c r="I36" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J36" s="13"/>
-      <c r="K36" s="14" t="s">
+      <c r="J36" s="15"/>
+      <c r="K36" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="L36" s="14"/>
+      <c r="L36" s="16"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="26"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="27"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="29"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="8"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="32"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="11"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="30"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="32"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="11"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="32"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="11"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="32"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="11"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="32"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="11"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="35"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="I12:L13"/>
+    <mergeCell ref="E15:L16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:L18"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="E19:L20"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="E23:L24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:L26"/>
+    <mergeCell ref="E27:L28"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="K33:L34"/>
     <mergeCell ref="A11:L11"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A39:L45"/>
@@ -1653,52 +1699,6 @@
     <mergeCell ref="K36:L37"/>
     <mergeCell ref="A30:L31"/>
     <mergeCell ref="A33:B34"/>
-    <mergeCell ref="E27:L28"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="E23:L24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:L26"/>
-    <mergeCell ref="E19:L20"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="I12:L13"/>
-    <mergeCell ref="E15:L16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:L18"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/15.VisualInspection.xlsx
+++ b/src/assets/worklog/15.VisualInspection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2854EA19-9B1B-4160-B17A-3B3D30DC4873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441018A-71A2-4C3B-8B6A-F63EB39F514C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
+    <workbookView xWindow="1455" yWindow="690" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -19,31 +19,35 @@
     <definedName name="approver">원본!$L$5</definedName>
     <definedName name="cellInputQuantity">원본!$I$12</definedName>
     <definedName name="cellNumberRange">원본!$C$12</definedName>
-    <definedName name="cellSizeDefectRemark">원본!$E$27</definedName>
-    <definedName name="cellSizeDiscardQuantity">원본!$C$27</definedName>
-    <definedName name="cleanCheck">원본!$G$36</definedName>
+    <definedName name="cellSizeLengthDefectRemark">원본!$E$29</definedName>
+    <definedName name="cellSizeLengthDiscardQuantity">원본!$C$29</definedName>
+    <definedName name="cellSizeThicknessDefectRemark">원본!$E$31</definedName>
+    <definedName name="cellSizeThicknessDiscardQuantity">원본!$C$31</definedName>
+    <definedName name="cellSizeWidthDefectRemark">원본!$E$27</definedName>
+    <definedName name="cellSizeWidthDiscardQuantity">원본!$C$27</definedName>
+    <definedName name="cleanCheck">원본!$G$40</definedName>
     <definedName name="dentDefectRemark">원본!$E$23</definedName>
     <definedName name="dentDiscardQuantity">원본!$C$23</definedName>
-    <definedName name="equipmentCheckResult">원본!$C$33</definedName>
-    <definedName name="equipmentIssue">원본!$K$33</definedName>
+    <definedName name="equipmentCheckResult">원본!$C$37</definedName>
+    <definedName name="equipmentIssue">원본!$K$37</definedName>
     <definedName name="foreignMatterDefectRemark">원본!$E$19</definedName>
     <definedName name="foreignMatterDiscardQuantity">원본!$C$19</definedName>
     <definedName name="gasDefectRemark">원본!$E$17</definedName>
     <definedName name="gasDiscardQuantity">원본!$C$17</definedName>
-    <definedName name="jigNumber">원본!$G$33</definedName>
+    <definedName name="jigNumber">원본!$G$37</definedName>
     <definedName name="leakCorrosionDefectRemark">원본!$E$25</definedName>
     <definedName name="leakCorrosionDiscardQuantity">원본!$C$25</definedName>
     <definedName name="line">원본!$C$9</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
     <definedName name="projectId">원본!$G$7</definedName>
-    <definedName name="remark">원본!$A$39</definedName>
+    <definedName name="remark">원본!$A$43</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
-    <definedName name="safety">원본!$K$36</definedName>
+    <definedName name="safety">원본!$K$40</definedName>
     <definedName name="scratchDefectRemark">원본!$E$21</definedName>
     <definedName name="scratchDiscardQuantity">원본!$C$21</definedName>
     <definedName name="shift">원본!$K$9</definedName>
-    <definedName name="tempHumi">원본!$C$36</definedName>
+    <definedName name="tempHumi">원본!$C$40</definedName>
     <definedName name="worker">원본!$K$7</definedName>
     <definedName name="writer">원본!$J$5</definedName>
   </definedNames>
@@ -68,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>작성</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -154,10 +158,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>전지 크기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>4. 공정 조건</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -228,6 +228,15 @@
   <si>
     <t>최종검사 작업 일지</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭</t>
+  </si>
+  <si>
+    <t>길이</t>
+  </si>
+  <si>
+    <t>두께</t>
   </si>
 </sst>
 </file>
@@ -237,7 +246,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,8 +295,16 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,8 +323,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -447,13 +470,139 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -463,6 +612,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -499,12 +711,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -523,61 +729,55 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -912,29 +1112,51 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="564" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0D9788BE-6EBE-4435-B231-8C2F02ACF12F}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="ko-KR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="ko-KR" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;09e46b6c-91e4-49ca-96b0-238044da21e5&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA102AAD-AE37-493E-B4D9-FE126E6236F2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="12" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="A1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,697 +1168,809 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="37" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="37" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="37" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="37"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="37" t="s">
+      <c r="F9" s="5"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="37"/>
-      <c r="K9" s="40" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="40"/>
+      <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="26"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="31" t="s">
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="17"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="20"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="17"/>
+    </row>
+    <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="58"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="50"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="49"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="50"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="47"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="45"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="49"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="50"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="47"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="45"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="44"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="46"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="53"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="38"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="41"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="26"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="14"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="26"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="33"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="36"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="25"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="28"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="25"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="28"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="25"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="28"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="25"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="28"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="25"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="25"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="28"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="19"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="22"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="5"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="15"/>
-      <c r="K33" s="29" t="s">
+      <c r="D40" s="14"/>
+      <c r="E40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="G40" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L33" s="16"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="5"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="H36" s="16"/>
-      <c r="I36" s="15" t="s">
+      <c r="L40" s="14"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J36" s="15"/>
-      <c r="K36" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36" s="16"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="8"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="11"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="11"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="26"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="11"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="29"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="11"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="32"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="14"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="32"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="32"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="32"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="32"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="33"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="68">
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A43:L49"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:F41"/>
+    <mergeCell ref="G40:H41"/>
+    <mergeCell ref="I40:J41"/>
+    <mergeCell ref="K40:L41"/>
+    <mergeCell ref="A34:L35"/>
+    <mergeCell ref="A37:B38"/>
+    <mergeCell ref="E27:L28"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:F38"/>
+    <mergeCell ref="G37:H38"/>
+    <mergeCell ref="I37:J38"/>
+    <mergeCell ref="K37:L38"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E29:L30"/>
+    <mergeCell ref="E31:L32"/>
+    <mergeCell ref="E23:L24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:L26"/>
+    <mergeCell ref="E19:L20"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="I12:L13"/>
+    <mergeCell ref="E15:L16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:L18"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:H13"/>
     <mergeCell ref="K9:L10"/>
     <mergeCell ref="A1:I5"/>
     <mergeCell ref="J2:J4"/>
@@ -1653,52 +1987,6 @@
     <mergeCell ref="E9:F10"/>
     <mergeCell ref="G9:H10"/>
     <mergeCell ref="I9:J10"/>
-    <mergeCell ref="I12:L13"/>
-    <mergeCell ref="E15:L16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:L18"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="E19:L20"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="E23:L24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:L26"/>
-    <mergeCell ref="E27:L28"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A39:L45"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:F37"/>
-    <mergeCell ref="G36:H37"/>
-    <mergeCell ref="I36:J37"/>
-    <mergeCell ref="K36:L37"/>
-    <mergeCell ref="A30:L31"/>
-    <mergeCell ref="A33:B34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/15.VisualInspection.xlsx
+++ b/src/assets/worklog/15.VisualInspection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6441018A-71A2-4C3B-8B6A-F63EB39F514C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B610026D-47BD-49F1-8E19-418D64B626EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="690" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
+    <workbookView xWindow="960" yWindow="360" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -25,29 +25,31 @@
     <definedName name="cellSizeThicknessDiscardQuantity">원본!$C$31</definedName>
     <definedName name="cellSizeWidthDefectRemark">원본!$E$27</definedName>
     <definedName name="cellSizeWidthDiscardQuantity">원본!$C$27</definedName>
-    <definedName name="cleanCheck">원본!$G$40</definedName>
+    <definedName name="cellWeightDefectRemark">원본!$E$33</definedName>
+    <definedName name="cellWeightDiscardQuantity">원본!$C$33</definedName>
+    <definedName name="cleanCheck">원본!$G$42</definedName>
     <definedName name="dentDefectRemark">원본!$E$23</definedName>
     <definedName name="dentDiscardQuantity">원본!$C$23</definedName>
-    <definedName name="equipmentCheckResult">원본!$C$37</definedName>
-    <definedName name="equipmentIssue">원본!$K$37</definedName>
+    <definedName name="equipmentCheckResult">원본!$C$39</definedName>
+    <definedName name="equipmentIssue">원본!$K$39</definedName>
     <definedName name="foreignMatterDefectRemark">원본!$E$19</definedName>
     <definedName name="foreignMatterDiscardQuantity">원본!$C$19</definedName>
     <definedName name="gasDefectRemark">원본!$E$17</definedName>
     <definedName name="gasDiscardQuantity">원본!$C$17</definedName>
-    <definedName name="jigNumber">원본!$G$37</definedName>
+    <definedName name="jigNumber">원본!$G$39</definedName>
     <definedName name="leakCorrosionDefectRemark">원본!$E$25</definedName>
     <definedName name="leakCorrosionDiscardQuantity">원본!$C$25</definedName>
     <definedName name="line">원본!$C$9</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
     <definedName name="projectId">원본!$G$7</definedName>
-    <definedName name="remark">원본!$A$43</definedName>
+    <definedName name="remark">원본!$A$45</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
-    <definedName name="safety">원본!$K$40</definedName>
+    <definedName name="safety">원본!$K$42</definedName>
     <definedName name="scratchDefectRemark">원본!$E$21</definedName>
     <definedName name="scratchDiscardQuantity">원본!$C$21</definedName>
     <definedName name="shift">원본!$K$9</definedName>
-    <definedName name="tempHumi">원본!$C$40</definedName>
+    <definedName name="tempHumi">원본!$C$42</definedName>
     <definedName name="worker">원본!$K$7</definedName>
     <definedName name="writer">원본!$J$5</definedName>
   </definedNames>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>작성</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -237,6 +239,9 @@
   </si>
   <si>
     <t>두께</t>
+  </si>
+  <si>
+    <t>무게</t>
   </si>
 </sst>
 </file>
@@ -330,7 +335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -550,59 +555,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -612,69 +571,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -711,51 +607,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -765,20 +616,131 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,7 +1076,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="564" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="550" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1139,24 +1101,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="12" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,809 +1130,790 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="26"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="5" t="s">
+      <c r="F7" s="48"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="5" t="s">
+      <c r="B9" s="48"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="48"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="3" t="s">
+      <c r="J9" s="48"/>
+      <c r="K9" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="51"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="26"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="22" t="s">
+      <c r="B12" s="48"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="26"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="9"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="44"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="12"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="47"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="37"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="20"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="40"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="37"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="20"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="40"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="17"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="20"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="40"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="17"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="37"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="20"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="17"/>
-    </row>
-    <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="54"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="58"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="37"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="40"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="50"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="28"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="50"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="45"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="33"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="50"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="28"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="45"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="33"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="44"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="46"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="28"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="55"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="32"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="59"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="57"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="53"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="36" t="s">
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="38"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="41"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="22"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="25"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="26"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="23" t="s">
+      <c r="B39" s="18"/>
+      <c r="C39" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="13" t="s">
+      <c r="D39" s="19"/>
+      <c r="E39" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="13" t="s">
+      <c r="F39" s="18"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="13"/>
-      <c r="K37" s="23" t="s">
+      <c r="J39" s="18"/>
+      <c r="K39" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="14"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="26"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14" t="s">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="13" t="s">
+      <c r="D42" s="19"/>
+      <c r="E42" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14" t="s">
+      <c r="F42" s="18"/>
+      <c r="G42" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="13" t="s">
+      <c r="H42" s="19"/>
+      <c r="I42" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="J40" s="13"/>
-      <c r="K40" s="14" t="s">
+      <c r="J42" s="18"/>
+      <c r="K42" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="L40" s="14"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
+      <c r="L42" s="19"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="26"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="29"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="32"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="30"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="32"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="8"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="30"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="32"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="32"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="11"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="32"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="11"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="35"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="11"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="11"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A43:L49"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:F41"/>
-    <mergeCell ref="G40:H41"/>
-    <mergeCell ref="I40:J41"/>
-    <mergeCell ref="K40:L41"/>
-    <mergeCell ref="A34:L35"/>
-    <mergeCell ref="A37:B38"/>
-    <mergeCell ref="E27:L28"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:F38"/>
-    <mergeCell ref="G37:H38"/>
-    <mergeCell ref="I37:J38"/>
-    <mergeCell ref="K37:L38"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E29:L30"/>
-    <mergeCell ref="E31:L32"/>
-    <mergeCell ref="E23:L24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:L26"/>
-    <mergeCell ref="E19:L20"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="I12:L13"/>
-    <mergeCell ref="E15:L16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:L18"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:H13"/>
+  <mergeCells count="71">
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:L34"/>
     <mergeCell ref="K9:L10"/>
     <mergeCell ref="A1:I5"/>
     <mergeCell ref="J2:J4"/>
@@ -1987,6 +1930,58 @@
     <mergeCell ref="E9:F10"/>
     <mergeCell ref="G9:H10"/>
     <mergeCell ref="I9:J10"/>
+    <mergeCell ref="I12:L13"/>
+    <mergeCell ref="E15:L16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:L18"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="E19:L20"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="E23:L24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:L26"/>
+    <mergeCell ref="E27:L28"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E29:L30"/>
+    <mergeCell ref="E31:L32"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A45:L51"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A42:B43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="E42:F43"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I42:J43"/>
+    <mergeCell ref="K42:L43"/>
+    <mergeCell ref="A36:L37"/>
+    <mergeCell ref="A39:B40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/15.VisualInspection.xlsx
+++ b/src/assets/worklog/15.VisualInspection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B610026D-47BD-49F1-8E19-418D64B626EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46F9C4F-C2F1-43EA-8533-2CB46C409B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="360" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
+    <workbookView xWindow="1200" yWindow="60" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이물질 외관</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>긁힘</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -242,6 +238,10 @@
   </si>
   <si>
     <t>무게</t>
+  </si>
+  <si>
+    <t>돌출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -561,7 +561,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -571,6 +571,111 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -616,12 +721,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -639,108 +738,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1108,17 +1105,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="A1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1130,787 +1127,842 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="48" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="48" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="48"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="48" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="48" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="51" t="s">
+      <c r="J9" s="15"/>
+      <c r="K9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="51"/>
+      <c r="L9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="5"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="40"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="50" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="32"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="40"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="50"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="42" t="s">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="27"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="30"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="27"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="30"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="23"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="27"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="30"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="27"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="28"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="30"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="27"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="30"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="35"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="33"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="35"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="33"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="35"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="37"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="33"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="35"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="52"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="55"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="56"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="58"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="40"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="24"/>
+      <c r="E39" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="23"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="23"/>
+      <c r="K39" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L39" s="24"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="40"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="23"/>
+      <c r="C42" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="44"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="47"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="37"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="40"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="37"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="40"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="37"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="40"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="37"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="37"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="40"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="28"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="28"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="33"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="28"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="33"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="28"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="55"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="32"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="57"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="17"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="22"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="25"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="5"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="18"/>
-      <c r="K39" s="29" t="s">
+      <c r="D42" s="24"/>
+      <c r="E42" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="24"/>
+      <c r="I42" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="23"/>
+      <c r="K42" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="L39" s="19"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="5"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="19"/>
-      <c r="E42" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="19"/>
-      <c r="I42" s="18" t="s">
+      <c r="L42" s="24"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="J42" s="18"/>
-      <c r="K42" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="L42" s="19"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="5"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="39"/>
+      <c r="L44" s="40"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="8"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="43"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="A46" s="44"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="46"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="11"/>
+      <c r="A47" s="44"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="46"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="11"/>
+      <c r="A48" s="44"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="46"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="11"/>
+      <c r="A49" s="44"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="46"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="11"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="46"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="14"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A45:L51"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A42:B43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="E42:F43"/>
+    <mergeCell ref="G42:H43"/>
+    <mergeCell ref="I42:J43"/>
+    <mergeCell ref="K42:L43"/>
+    <mergeCell ref="A36:L37"/>
+    <mergeCell ref="A39:B40"/>
+    <mergeCell ref="E27:L28"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E29:L30"/>
+    <mergeCell ref="E31:L32"/>
+    <mergeCell ref="E23:L24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:L26"/>
+    <mergeCell ref="E19:L20"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:L18"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="I12:L13"/>
+    <mergeCell ref="E15:L16"/>
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="A33:B34"/>
     <mergeCell ref="C33:D34"/>
     <mergeCell ref="E33:L34"/>
@@ -1927,61 +1979,6 @@
     <mergeCell ref="K7:L8"/>
     <mergeCell ref="A9:B10"/>
     <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="I12:L13"/>
-    <mergeCell ref="E15:L16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:L18"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="E19:L20"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="E23:L24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:L26"/>
-    <mergeCell ref="E27:L28"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E29:L30"/>
-    <mergeCell ref="E31:L32"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A45:L51"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A38:L38"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A42:B43"/>
-    <mergeCell ref="C42:D43"/>
-    <mergeCell ref="E42:F43"/>
-    <mergeCell ref="G42:H43"/>
-    <mergeCell ref="I42:J43"/>
-    <mergeCell ref="K42:L43"/>
-    <mergeCell ref="A36:L37"/>
-    <mergeCell ref="A39:B40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/15.VisualInspection.xlsx
+++ b/src/assets/worklog/15.VisualInspection.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46F9C4F-C2F1-43EA-8533-2CB46C409B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CF13F2-748A-454A-B7F1-A58E6A63CC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="60" windowWidth="25290" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
+    <workbookView xWindow="1320" yWindow="330" windowWidth="25260" windowHeight="15045" xr2:uid="{52CEF874-3BDC-4997-AD6D-9132F1472711}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -571,111 +571,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -721,6 +616,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -737,6 +638,105 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1105,17 +1105,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,787 +1127,842 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="40"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="15" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="15" t="s">
+      <c r="F7" s="39"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="15" t="s">
+      <c r="B9" s="39"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="15" t="s">
+      <c r="F9" s="39"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="13" t="s">
+      <c r="J9" s="39"/>
+      <c r="K9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="13"/>
+      <c r="L9" s="46"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="40"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="40"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="5"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="41"/>
+      <c r="E15" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="19"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="41"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="22"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="43"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="27"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="30"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="27"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="35"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="30"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="38"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="27"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="35"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="30"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="38"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="27"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="35"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="30"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="38"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="27"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="35"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="30"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="38"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="35"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="28"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="35"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="28"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="4"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="32"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="35"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="28"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="4"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="32"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="35"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="28"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="8"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="55"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="10"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="58"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
-      <c r="L35" s="52"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="17"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="54"/>
-      <c r="L36" s="55"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="22"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="56"/>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="57"/>
-      <c r="L37" s="58"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="25"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="40"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="5"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="36" t="s">
+      <c r="B39" s="18"/>
+      <c r="C39" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="23" t="s">
+      <c r="D39" s="19"/>
+      <c r="E39" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F39" s="23"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="23" t="s">
+      <c r="F39" s="18"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="23"/>
-      <c r="K39" s="36" t="s">
+      <c r="J39" s="18"/>
+      <c r="K39" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="L39" s="24"/>
+      <c r="L39" s="19"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="23"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="38" t="s">
+      <c r="A41" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="40"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="5"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="24" t="s">
+      <c r="B42" s="18"/>
+      <c r="C42" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="24"/>
-      <c r="E42" s="23" t="s">
+      <c r="D42" s="19"/>
+      <c r="E42" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="23"/>
-      <c r="G42" s="24" t="s">
+      <c r="F42" s="18"/>
+      <c r="G42" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="24"/>
-      <c r="I42" s="23" t="s">
+      <c r="H42" s="19"/>
+      <c r="I42" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J42" s="23"/>
-      <c r="K42" s="24" t="s">
+      <c r="J42" s="18"/>
+      <c r="K42" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="L42" s="24"/>
+      <c r="L42" s="19"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="23"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="40"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="5"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="43"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="8"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="44"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="46"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="11"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="44"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="46"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="11"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="44"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="46"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="11"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="44"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="46"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="46"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="11"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="47"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="49"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="I12:L13"/>
+    <mergeCell ref="E15:L16"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:L18"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="E19:L20"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:L22"/>
+    <mergeCell ref="E23:L24"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:L26"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E29:L30"/>
+    <mergeCell ref="E31:L32"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:L34"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:F40"/>
+    <mergeCell ref="G39:H40"/>
     <mergeCell ref="A6:L6"/>
     <mergeCell ref="A45:L51"/>
     <mergeCell ref="A35:L35"/>
@@ -1924,61 +1979,6 @@
     <mergeCell ref="A36:L37"/>
     <mergeCell ref="A39:B40"/>
     <mergeCell ref="E27:L28"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E29:L30"/>
-    <mergeCell ref="E31:L32"/>
-    <mergeCell ref="E23:L24"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:L26"/>
-    <mergeCell ref="E19:L20"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:L22"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:L18"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="I12:L13"/>
-    <mergeCell ref="E15:L16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:L34"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
